--- a/zaini_case_audit_output/outputs/excel/02_study_vs_drive_comparison.xlsx
+++ b/zaini_case_audit_output/outputs/excel/02_study_vs_drive_comparison.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -457,6 +457,4230 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>وسم مراجعة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>مذكرة توضيحية من المدعي ـ 06-03-1445</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>إخطار بمطالبة مالية مقدم بتاريخ 14/7/2024م والخاص بالمبلغ المحكوم به للسيد/ عدنان زيني، في صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (96,779,270) ريال ـ 13/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>إخطار بمطالبة مالية مقدم بتاريخ 14/7/2024م والخاص بالمبلغ المحكوم به للسيد/ عدنان زيني، في صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (96,779,270) ريال ـ 13/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ملف دراسة دفع بعدم صفة المدعي/ عدنان في الدعوى لكون المورث قد امتدت حياته عقب العقد بسبع سنوات دون أن يطعن في العقد. ـ —</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ملف دراسة دفع بعدم صفة المدعي/ عدنان في الدعوى لكون المورث قد امتدت حياته عقب العقد بسبع سنوات دون أن يطعن في العقد. ـ —</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>التماس الشيخ أسامة ـ 20-10-2025 ـ أبو راشد</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>التماس الشيخ أسامة ـ 20-10-2025 ـ أبو راشد</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ـ الاستئناف الثانية ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>تفاصيل دعوى عدنان ضد أسامة ـ موعدها 03-01-1443</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>تفاصيل دعوى عدنان ضد أسامة ـ موعدها 03-01-1443</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>سداد عقد المحاصة (Excel)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>سداد عقد المحاصة (Excel)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>تفاصيل شكوى المجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>صك الحكم رقم (4431025114) وتاريخ 1/1/1445هـ الصادر عن الدائرة الأولى بالمحكمة التجارية بجدة في الدعوى المقيدة برقم (42824717) وتاريخ 25/12/1442هـ ـ 1/1/1445هـ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>صك الحكم رقم (4431025114) وتاريخ 1/1/1445هـ الصادر عن الدائرة الأولى بالمحكمة التجارية بجدة في الدعوى المقيدة برقم (42824717) وتاريخ 25/12/1442هـ ـ 1/1/1445هـ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>عقد بيع حصص الشيخ احمد زيني في شركة احمد زيني التجارية الى اسامة ـ 20-09-1431.pdf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>عقد بيع حصص الشيخ احمد زيني في شركة احمد زيني التجارية الى اسامة ـ 20-09-1431.pdf</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل ـ جديدة 2 ـ 05-11-1445 (وورد)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>تقرير العيوطي — وُجد بتاريخ 11/06/2026م ضمن مجلد مرفقات مذكرة الالتماس بين المورث وعبد الله آبار، وتقترح الدراسة نقض تقرير أبو غزالة به ـ —</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>تقرير العيوطي — وُجد بتاريخ 11/06/2026م ضمن مجلد مرفقات مذكرة الالتماس بين المورث وعبد الله آبار، وتقترح الدراسة نقض تقرير أبو غزالة به ـ —</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية ـ 16-08-1445</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية ـ 16-08-1445</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>جزء من مسحوبات مصروفات الشيخ أحمد</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>جزء من مسحوبات مصروفات الشيخ أحمد</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>تفاصيل موعد دعوى عدنان ضد أسامة</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>تفاصيل موعد دعوى عدنان ضد أسامة</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>مرفق 1 ـ مذكرة عزام خوج ـ 05-07-1434</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>مذكرة طلب النقض ـ الحجيلان ـ 13-07-1446 ـ أحيلت</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>مذكرة طلب النقض ـ الحجيلان ـ 13-07-1446 ـ أحيلت</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل (وورد)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل (وورد)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>مذكرة نقض؟ .docx</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>مذكرة نقض؟ .docx</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>مذكرة الاستئناف اعتراضاً على الدرجة الأولى ـ 15-07-1447</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>مذكرة الاستئناف اعتراضاً على الدرجة الأولى ـ 15-07-1447</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>صك حكم التخارج في شركات احمد زيني و اولاده ـ 02-12-1432 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>صك حكم التخارج في شركات احمد زيني و اولاده ـ 02-12-1432 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>صورة التقديم (jpg)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>صورة التقديم (jpg)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>سند براءة الذمة من عاتقة ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>حكم الدعيلج بإرجاع القضية 3218883 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>تقرير جلسة القضية ـ 17-12-2024</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>تقرير جلسة القضية ـ 17-12-2024</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>صورة التقديم (pdf)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>صورة التقديم (pdf)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>المسحوبات 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>المسحوبات 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>عقد البيع 1431-9-20 حصص الشيخ احمد زيني رحمه الله في شركة احمد زيني التجارية الى الشيخ اسامة ـ القرعاوي 120 مليون.pdf</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>عقد البيع 1431-9-20 حصص الشيخ احمد زيني رحمه الله في شركة احمد زيني التجارية الى الشيخ اسامة ـ القرعاوي 120 مليون.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى ا</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى ا</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>محضر جلسة دعوى عدنان ضد أسامة</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>محضر جلسة دعوى عدنان ضد أسامة</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>تفاصيل التقديم ـ موقع توارد</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>رد مجلس القضاء الأعلى على الشكوى ـ 199058</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>شكوى لدى المجلس الأعلى للقضاء ضد الدائرة. ـ —</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>التماس ضد الحكم ـ نسخة أولى</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>تفاصيل الشكوى</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>تفاصيل الشكوى</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>المسحوبات 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>المسحوبات 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>وكالة الجدة عاتقة الى محمد الثعلي ـ في 19-03-1445 ـ تنتهي 19-03-1446.pdf</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>وكالة الجدة عاتقة الى محمد الثعلي ـ في 19-03-1445 ـ تنتهي 19-03-1446.pdf</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>طلب النقض 23-09-1445 ـ رقم 45117602 ـ محال للعليا</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>طلب النقض 23-09-1445 ـ رقم 45117602 ـ محال للعليا</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>مذكرة التماس الشهري 13-07-1445 ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>مذكرة التماس الشهري 13-07-1445 ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>طلب النقض الأخير ـ 07-10-1447</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>طلب النقض الأخير ـ 07-10-1447</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>المسحوبات 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>المسحوبات 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>تفاصيل طلب موعد مع وزير العدل ـ 19-06-1445</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>تفاصيل طلب موعد مع وزير العدل ـ 19-06-1445</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>موجز الشكوى للمجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>موجز الشكوى للمجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>المسحوبات 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>المسحوبات 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>طلب الشكوى للمجلس الأعلى (صورة)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>قرار تطبيق المادة (46) على السيد/ أسامة الزيني بخصوص طلب التنفيذ المقدم من السيد/ عدنان. ـ —</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>قرار تطبيق المادة (46) على السيد/ أسامة الزيني بخصوص طلب التنفيذ المقدم من السيد/ عدنان. ـ —</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1431 (rar)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1431 (rar)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>صورة رفض مذكرة طلب النقض ـ 10-04-1445</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>صورة رفض مذكرة طلب النقض ـ 10-04-1445</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>مذكرة من المحامي السديري 20-02-1445 ـ الاعتراض على تقرير ابو غزالة.pdf</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>مذكرة من المحامي السديري 20-02-1445 ـ الاعتراض على تقرير ابو غزالة.pdf</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ما يفيد استلام السيد/ سليمان السديري أصل عقد البيع موضوع الدعوى والمبرم بين السيد/ أسامة زيني والمورث. ـ —</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ما يفيد استلام السيد/ سليمان السديري أصل عقد البيع موضوع الدعوى والمبرم بين السيد/ أسامة زيني والمورث. ـ —</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ملف المسحوبات (Excel)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ملف المسحوبات (Excel)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>-05-11~1.DOC.docx</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>-05-11~1.DOC.docx</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية على قضية 42824717 ـ التماس ـ تناقض الحكم - 28-01-2026.pdf</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>محضر اجتماع تقسيم شركات ابار وزيني و شيكات الامير احمد و بيان شيكات القروض البنكية.pdf</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>محضر اجتماع تقسيم شركات ابار وزيني و شيكات الامير احمد و بيان شيكات القروض البنكية.pdf</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>مرفق رقم 5 ـ مذكرة جوابية من مكتب المحامي ابو راشد في الدعوى رقم 4717  بتاريخ 06-03-1443هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل ـ 13-11-1445</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل ـ 13-11-1445</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>4257FF~1.DOC (مذكرة قديمة بترميز تالف)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>آلية تنفيذ بتاريخ 09/02/1434هـ الموافق 22/12/2012م لدى فضيلة القاضي/ علي القريقري، قاضي التنفيذ بالمحكمة العامة بجدة [وذلك فيما يتعلق بنقل كل من طرفي النزاع الشركات التي اختص بها ك</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>آلية تنفيذ بتاريخ 09/02/1434هـ الموافق 22/12/2012م لدى فضيلة القاضي/ علي القريقري، قاضي التنفيذ بالمحكمة العامة بجدة [وذلك فيما يتعلق بنقل كل من طرفي النزاع الشركات التي اختص بها ك</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>إقرار من السيدة/ عاتقة محمد يحي حرازي مؤرخ في 04/03/1445هـ، ممهور ببصمتها، بأنها أوكلت المحامِ (محمد فواز الثعلي) وكيلًا عنها، وعدم صحة الادعاء بحجزها ـ 04/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>إقرار من السيدة/ عاتقة محمد يحي حرازي مؤرخ في 04/03/1445هـ، ممهور ببصمتها، بأنها أوكلت المحامِ (محمد فواز الثعلي) وكيلًا عنها، وعدم صحة الادعاء بحجزها ـ 04/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>مصاريف المزرعة (Excel)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>مصاريف المزرعة (Excel)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>حكم نهائي بنقض حكم إبراء الذمة ـ 22-07-1447</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>حكم نهائي بنقض حكم إبراء الذمة ـ 22-07-1447</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ملخص الشكوى لولي العهد (وورد)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ملخص الشكوى لولي العهد (وورد)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>المسحوبات 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>المسحوبات 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>طلب إعادة فتح الشكوى المقيدة برقم (199058) وتاريخ 18/06/1445هـ لدى المجلس الأعلى للقضاء ـ 18/06/1445هـ</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>طلب إعادة فتح الشكوى المقيدة برقم (199058) وتاريخ 18/06/1445هـ لدى المجلس الأعلى للقضاء ـ 18/06/1445هـ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>تفاصيل إخطار المطالبة المالية بمبلغ 96,779,270</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>تفاصيل إخطار المطالبة المالية بمبلغ 96,779,270</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>التماس في الدعوى ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>التماس في الدعوى ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>مرفق (1) القروض (zip)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>مرفق (1) القروض (zip)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>مرفق 8 ـ مذكرة أبو راشد ـ 25-04-1443</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>مرفق 8 ـ مذكرة أبو راشد ـ 25-04-1443</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>صك الحكم رقم (4630548401) وتاريخ 18/06/1446هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، والقاضي بعدم قبول الالتماس المقدم بالطلب رقم (4611037394) وتاريخ 02/06/1446ه</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>صك الحكم رقم (4630548401) وتاريخ 18/06/1446هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، والقاضي بعدم قبول الالتماس المقدم بالطلب رقم (4611037394) وتاريخ 02/06/1446ه</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (3)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (3)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>جزء من مصروفات فيلا الوادي</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>جزء من مصروفات فيلا الوادي</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>مرفقات تقييم شركة احمد زيني التجارية مرة بمبلغ 68 مليون ومرة بمبلغ 79 مليون.pdf</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>مرفقات تقييم شركة احمد زيني التجارية مرة بمبلغ 68 مليون ومرة بمبلغ 79 مليون.pdf</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>فلة الوادي 2015 (rar)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>فلة الوادي 2015 (rar)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>طلب التماس 20-10-2025 ـ ناجز (صورة)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>طلب التماس 20-10-2025 ـ ناجز (صورة)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من المدعي ـ 28-08-1447</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>طلب النقض من المحكمة العليا ـ 25-02-1445</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>طلب النقض من المحكمة العليا ـ 25-02-1445</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>تفاصيل التقديم ـ صدرت للمجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>المسحوبات 2015 (zip)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>المسحوبات 2015 (zip)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>مرفق 6 ـ مذكرة أبو راشد ـ 15-03-1443</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>مرفقات الشكوى</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>تعذر التقديم الإلكتروني بمجلس القضاء ـ 29-10-2024</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>صفحة 1 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>صفحة 1 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان زيني ضد الشيخ أسامة ـ 401024501215577 ـ 16-03-1445</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>موجز إعادة فتح الشكوى</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>موجز إعادة فتح الشكوى</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>طلب الاعتراض بالنقض ـ 2</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>طلب الاعتراض بالنقض ـ 2</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>تقرير خبرة (المرحلة الأولى) صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 27/6/2011م ـ 27/6/2011م</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>طلب التماس 20-10-2025 ـ ناجز</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>طلب التماس 20-10-2025 ـ ناجز</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>تقديم التماس إعادة نظر في القضية من عدنان وعاتقة ـ 03-12-2024</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>تقديم التماس إعادة نظر في القضية من عدنان وعاتقة ـ 03-12-2024</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>مذكرة الالتماس ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>مذكرة الالتماس ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ردود على حكم الالتماس 717</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ردود على حكم الالتماس 717</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>ملخص تقرير خبرة مقدم إلى المحكمة الإدارية العامة بجدة الدائرة السابعة عشر صادر عن مكتب "طلال أبو غزالة وشركاه" مؤرخ 5/10/2011م ـ 5/10/2011م</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>جزء من مصروفات المزرعة</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>جزء من مصروفات المزرعة</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة (وورد)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة (وورد)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>حكما إثبات التنازل والتخارج وإبراء الذمة ومستندات التنازل</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>حكما إثبات التنازل والتخارج وإبراء الذمة ومستندات التنازل</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (1)</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (1)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>صفحة 2 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>صفحة 2 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>مرفق 3 ـ مذكرة أبو راشد ـ 23-01-1443</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>مرفق 7 ـ مذكرة أبو راشد ـ 27-03-1443</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>مرفق 7 ـ مذكرة أبو راشد ـ 27-03-1443</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1433 (rar)</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1433 (rar)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>عقود تعيين الشيخ أسامة في إدارة الشركات</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>عقود تعيين الشيخ أسامة في إدارة الشركات</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>محضر رفع التصرف على صك أرض التنس بموجب طلب الإفلاس من عدنان رقم (405034600788314) وتاريخ 23/03/1446هـ. ـ 23/03/1446هـ</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>محضر رفع التصرف على صك أرض التنس بموجب طلب الإفلاس من عدنان رقم (405034600788314) وتاريخ 23/03/1446هـ. ـ 23/03/1446هـ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى لحجز موعد مع الوزير</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>مرفق 4 ـ مذكرة أبو راشد ـ 28-01-1443</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>مرفق 4 ـ مذكرة أبو راشد ـ 28-01-1443</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>مذكرة النقض للعليا 23-09-1445 ـ مرفق حكم التخارج</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>تقرير أبو غزالة ـ المرحلة الأولى (أولاً وثانياً)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>سند براءة ذمة من السيدة/ عاتقة مؤرخ في 25/08/1445هـ الموافق 06/03/2024م بخصوص المبلغ المستحق لها بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال. ـ 25/</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>تذكرة تقديم طلب التماس إعادة نظر في القضية رقم (42824717) مقيد برقم (4611037394) وتاريخ 02/06/1446هـ ـ 02/06/1446هـ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>حكم القاضي الدعيلج بإرجاع القضية رقم 3218883 ـ 25-10-1438</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>مصاريف فيلا الوادي (Excel)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>مصاريف فيلا الوادي (Excel)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>مسودة التماس إعادة النظر المقدم على صك الاستئناف الصادر في الدعوى رقم (42824717) وتاريخ 25/12/1442هـ. ـ 25/12/1442هـ</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>مسودة التماس إعادة النظر المقدم على صك الاستئناف الصادر في الدعوى رقم (42824717) وتاريخ 25/12/1442هـ. ـ 25/12/1442هـ</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من الملتمس ضدهم (عدنان وعاتقة)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من الملتمس ضدهم (عدنان وعاتقة)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>مرفق 2 ـ مذكرة أبو راشد ـ 04-01-1443</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>مرفق 2 ـ مذكرة أبو راشد ـ 04-01-1443</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (2)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (2)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>ملف القروض (Excel)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>ملف القروض (Excel)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>طلب إعادة فتح الشكوى (صورة)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>طلب إعادة فتح الشكوى (صورة)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامة</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامة</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>طلب تنفيذ مقدم من السيدة/ عاتقة ضد السيد/ أسامة فيما يتعلق بالمبلغ المحكوم لها به بموجب صك الحكم رقم (4530241622) وتاريخ 13/03/1445هـ، وقدره (27,651,219) ريال ـ 13/03/1445هـ</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ الوالدة عاتقة ضد الشيخ أسامة ـ 401024501240718 ـ 08-04-1445 ـ منتهي</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>محضر تفويض المحكمة وكيل السيد/ عدنان تحديث صك أرض الروضة بموجب طلب الإفلاس المقدم من عدنان رقم (405034600730696) وتاريخ 24/1/1446هـ ـ 24/1/1446هـ</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>محضر تفويض المحكمة وكيل السيد/ عدنان تحديث صك أرض الروضة بموجب طلب الإفلاس المقدم من عدنان رقم (405034600730696) وتاريخ 24/1/1446هـ ـ 24/1/1446هـ</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ملف مؤقت tmp</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ملف مؤقت tmp</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>التماس الشيخ أسامة ـ 29-04-1447</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>التماس الشيخ أسامة ـ 29-04-1447</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>مختصر الشكوى المقدمة بموقع المجلس الأعلى</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>صفحة 3 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>صفحة 3 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>المسحوبات 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>المسحوبات 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>طلب الاعتراض على حكم الدرجة الأولى ـ 15-07-1447 ـ ناجز</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>طلب الاعتراض على حكم الدرجة الأولى ـ 15-07-1447 ـ ناجز</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>طلب النقض على صك الاستئناف الثانية</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>جدول مواعيد تبادل المذكرات والمستندات في الدعوى رقم (4717) لعام 1442هـ أمام الدائرة التجارية الأولى في الدعوى المقامة من عدنان زيني ضد عاتقة وآخرون. ـ —</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>جدول مواعيد تبادل المذكرات والمستندات في الدعوى رقم (4717) لعام 1442هـ أمام الدائرة التجارية الأولى في الدعوى المقامة من عدنان زيني ضد عاتقة وآخرون. ـ —</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>مذكرة النقض للعليا 10-04-1445 ـ مرفق عقود التخارج</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>مذكرة النقض للعليا 10-04-1445 ـ مرفق عقود التخارج</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ دائرة الاستئناف الثانية</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>لائحة المدعي بتفصيل مبلغ الحكم الابتدائي ـ 01-02-1445</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>لائحة المدعي بتفصيل مبلغ الحكم الابتدائي ـ 01-02-1445</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>مذكرة جوابية من عدنان وعاتقة ـ 16-11-1444 ـ مرفق تقييم</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1432 (rar)</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1432 (rar)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>مذكرة إلحاقية ـ تناقض الحكم ـ 28-01-2026 (وورد)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>مذكرة التماس إلحاقية ـ 08-08-1445</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>مذكرة التماس إلحاقية ـ 08-08-1445</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>خطاب وزارة التجارة بتوثيق تخارج المدعين من شركة احمد زيني واولاده ـ 10-02-1434 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>خطاب وزارة التجارة بتوثيق تخارج المدعين من شركة احمد زيني واولاده ـ 10-02-1434 هـ.pdf</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>مذكرة طلب النقض على الحكم النهائي</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>
       </c>
     </row>
@@ -513,7 +4737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -541,776 +4765,6 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>وسم مراجعة</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>صك حكم التخارج في شركات احمد زيني و اولاده ـ 02-12-1432 هـ.pdf</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>خطاب وزارة التجارة بتوثيق تخارج المدعين من شركة احمد زيني واولاده ـ 10-02-1434 هـ.pdf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 30 يوم 17-11-1444 هـ للدعوى رقم 42824717 تمسك المدعي بالتقييم وليس تزوير العقد.pdf</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>جلسة يوم 01-08-1444 ـ قضية 42824717 ـ ارسال القاضي مستندات موقع من الشيخ احمد الى الادلة الجنائية.pdf</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 31 يوم 24-11-1444 هـ للدعوى رقم 42824717 طلب المدعى عليه تقديم العقد للادلة الجنائية.pdf</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 29 يوم 10-11-1444 هـ للدعوى رقم 42824717 طلب الادلة الجنائية اصل العقد.pdf</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ضبط الجلسة رقم 18 بتاريخ 27-01-1444هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>مذكرة نقض؟ .docx</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>مذكرة من المحامي السديري 20-02-1445 ـ الاعتراض على تقرير ابو غزالة.pdf</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>الإيميل الوارد من الدكتور محمد البنا بشأن دراسة الحكمين في قضية 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>شكوى التفتيش القضائي قضية 42824717 ـ 16-07-2025 ـ موقع.PDF</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>تقرير عن اسباب رفض النقض قضية 42824717 عدنان زيني ضد الشيخ أسامة زيني 17-04-2025.pdf</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>وكالة الجدة عاتقة الى محمد الثعلي ـ في 19-03-1445 ـ تنتهي 19-03-1446.pdf</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>تقرير بشأن استلام أصل عقد بيع حصص شركة أحمد زيني التجارية 16-07-1446.pdf</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>عقد بيع حصص الشيخ احمد زيني في شركة احمد زيني التجارية الى اسامة ـ 20-09-1431.pdf</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>مرفقات تقييم شركة احمد زيني التجارية مرة بمبلغ 68 مليون ومرة بمبلغ 79 مليون.pdf</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>صحيفة دعوى عدنان ضد اسامة زيني ـ بطلان بيع حصة شركة احمد زيني التجارية الى اسامة زيني ـ 42824717 ـ 17-12-1442.pdf</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>حكم الولاية على الشيخ أحمد زيني من القاضي الزايدي مصدق من الاستئناف - 26-07-1434.pdf</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>حكم برفض الولاية على الشيخ أحمد زيني من القاضي اللحيدان ـ 08-06-1433هـ.pdf</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>ملحق تنازل الشيخ احمد زيني عن كامل حصصه الى الشيخ اسامة في شركة احمد زيني التجارية ـ 16-10-1431.pdf</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>تعذّر العثور على نص الدراسة - لم تُجرَ المقارنة</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>
       </c>
     </row>
@@ -1370,7 +4824,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf | صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf | حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1400,7 +4854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1440,12 +4894,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>حكم نهائي الشيخ اسامة زيني ـ 42824717 - 25-08-1445 رفض الالتماس.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>صك حكم نهائي الشيخ اسامة زيني ـ دعوى 42824717 - 25-08-1445 هـ رفض الالتماس.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1467,17 +4921,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تفاصيل دعوى عدنان ضد أسامة ـ موعدها 03-01-1443</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>تفاصيل موعد دعوى عدنان ضد أسامة</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1494,17 +4948,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1521,17 +4975,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>طلب التماس 20-10-2025 ـ ناجز (صورة)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>طلب التماس 20-10-2025 ـ ناجز</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1548,12 +5002,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1575,12 +5029,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1602,12 +5056,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1629,12 +5083,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1656,12 +5110,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1683,12 +5137,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1742,7 +5196,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1769,7 +5223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1791,12 +5245,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1818,12 +5272,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1845,12 +5299,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1872,12 +5326,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1899,12 +5353,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1926,12 +5380,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1953,12 +5407,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1980,12 +5434,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2007,12 +5461,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2034,12 +5488,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2061,12 +5515,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2088,12 +5542,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2115,12 +5569,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2142,12 +5596,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2169,12 +5623,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2201,7 +5655,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2228,7 +5682,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2255,7 +5709,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2277,12 +5731,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2304,12 +5758,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2331,12 +5785,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2363,7 +5817,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2390,7 +5844,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2412,12 +5866,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2439,12 +5893,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2466,7 +5920,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2498,7 +5952,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2520,12 +5974,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2547,12 +6001,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2574,12 +6028,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2601,12 +6055,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2628,7 +6082,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2655,25 +6109,1078 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1431 (zip)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1432 (zip)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1433 (zip)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1434 (zip)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1435 (zip)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>مزرعة الوادي 1436 (zip)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1431 (rar)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1432 (rar)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1431 (rar)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1433 (rar)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1431 (rar)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>فلة الوادي 2015 (rar)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1432 (rar)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1433 (rar)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1432 (rar)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>فلة الوادي 2015 (rar)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>فلة الوادي 1433 (rar)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>فلة الوادي 2015 (rar)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ نسخة</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>التماس على الحكم النهائي ـ نسخة ثانية</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عاتقة ـ نسخة</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>أمر تنفيذ عدنان ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل (وورد)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (1)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (2)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (1)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (3)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (2)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>صورة تقديم 21-05-2024 (3)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>الشكوى (وورد)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة (وورد)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>صفحة 1 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>صفحة 2 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>صفحة 1 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>صفحة 3 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>صفحة 2 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>صفحة 3 من تقديم الشكوى</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة (وورد)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>الشكوى الرابعة</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/02_study_vs_drive_comparison.xlsx
+++ b/zaini_case_audit_output/outputs/excel/02_study_vs_drive_comparison.xlsx
@@ -683,12 +683,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>صك الحكم رقم (4431025114) وتاريخ 1/1/1445هـ الصادر عن الدائرة الأولى بالمحكمة التجارية بجدة في الدعوى المقيدة برقم (42824717) وتاريخ 25/12/1442هـ ـ 1/1/1445هـ</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>صك الحكم رقم (4431025114) وتاريخ 1/1/1445هـ الصادر عن الدائرة الأولى بالمحكمة التجارية بجدة في الدعوى المقيدة برقم (42824717) وتاريخ 25/12/1442هـ ـ 1/1/1445هـ</t>
+          <t>صك حكم ابتدائي ضد الشيخ اسامة زيني في القضية رقم 42824717 في 01-01-1445 هـ.pdf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -771,12 +771,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>تقرير العيوطي — وُجد بتاريخ 11/06/2026م ضمن مجلد مرفقات مذكرة الالتماس بين المورث وعبد الله آبار، وتقترح الدراسة نقض تقرير أبو غزالة به ـ —</t>
+          <t>تقييم العيوطي للشركات.pdf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>تقرير العيوطي — وُجد بتاريخ 11/06/2026م ضمن مجلد مرفقات مذكرة الالتماس بين المورث وعبد الله آبار، وتقترح الدراسة نقض تقرير أبو غزالة به ـ —</t>
+          <t>تقييم العيوطي للشركات.pdf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -815,12 +815,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>مذكرة جوابية ـ 16-08-1445</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>مذكرة جوابية ـ 16-08-1445</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -837,12 +837,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>جزء من مسحوبات مصروفات الشيخ أحمد</t>
+          <t>جزء من مسحوبات مصروفات الشيخ احمد زيني رحمه الله.pdf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>جزء من مسحوبات مصروفات الشيخ أحمد</t>
+          <t>جزء من مسحوبات مصروفات الشيخ احمد زيني رحمه الله.pdf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -969,12 +969,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل (وورد)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ قضية رقم 42824717.docx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1277,12 +1277,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى ا</t>
+          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى المقيدة برقم (42824717) وقضية أرض التنس.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى ا</t>
+          <t>تقرير من شركة "صلاح الحجيلان للمحاماة والاستشارات القانونية مؤرخ في 10/02/1447هـ الموافق 04/08/2025م بشأن تقديم شكوى للديوان الملكي بمحافظة جدة للمخالفات التي وقعت عند نظر الدعوى المقيدة برقم (42824717) وقضية أرض التنس.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1585,12 +1585,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>مذكرة التماس الشهري 13-07-1445 ومرفقاتها</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>مذكرة التماس الشهري 13-07-1445 ومرفقاتها</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1739,12 +1739,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
+          <t>تقديم مذكرة جوابية على المدعي عدنان ضد الشيخ اسامة زيني - 02-09-1447 - 42824717.pdf</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1761,12 +1761,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>طلب النقض الأخير ـ 07-10-1447</t>
+          <t>طلب النقض الاحير المقدم في 07-10-1447 ـ القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>طلب النقض الأخير ـ 07-10-1447</t>
+          <t>طلب النقض الاحير المقدم في 07-10-1447 ـ القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1805,12 +1805,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل ـ 19-06-1445</t>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>تفاصيل طلب موعد مع وزير العدل ـ 19-06-1445</t>
+          <t>تفاصيل طلب موعد مع وزير العدل بتاريخ 19-06-1445.pdf</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1827,12 +1827,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>موجز الشكوى للمجلس الأعلى</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>موجز الشكوى للمجلس الأعلى</t>
+          <t>موجز عن شكوى الشيخ اسامة زيني رقم 230747621 في 30-04-1445هـ الى المجلس الأعلى للقضاء ـ في القضية 42824717.pdf</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2245,12 +2245,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ 13-11-1445</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل ـ 13-11-1445</t>
+          <t>شكوى اسامة زيني لوزير العدل 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2355,12 +2355,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>آلية تنفيذ بتاريخ 09/02/1434هـ الموافق 22/12/2012م لدى فضيلة القاضي/ علي القريقري، قاضي التنفيذ بالمحكمة العامة بجدة [وذلك فيما يتعلق بنقل كل من طرفي النزاع الشركات التي اختص بها ك</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>آلية تنفيذ بتاريخ 09/02/1434هـ الموافق 22/12/2012م لدى فضيلة القاضي/ علي القريقري، قاضي التنفيذ بالمحكمة العامة بجدة [وذلك فيما يتعلق بنقل كل من طرفي النزاع الشركات التي اختص بها ك</t>
+          <t>آلية تنفيذ لدى القاضي علي القريقري ـ موقعه من جميع الاطراف.pdf</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2377,12 +2377,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>إقرار من السيدة/ عاتقة محمد يحي حرازي مؤرخ في 04/03/1445هـ، ممهور ببصمتها، بأنها أوكلت المحامِ (محمد فواز الثعلي) وكيلًا عنها، وعدم صحة الادعاء بحجزها ـ 04/03/1445هـ</t>
+          <t>اقرار من الوالدة عاتقة توكيل الثعلي في الدعوى 42824717 ضد اسامة زيني ـ 04-03-1445.pdf</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>إقرار من السيدة/ عاتقة محمد يحي حرازي مؤرخ في 04/03/1445هـ، ممهور ببصمتها، بأنها أوكلت المحامِ (محمد فواز الثعلي) وكيلًا عنها، وعدم صحة الادعاء بحجزها ـ 04/03/1445هـ</t>
+          <t>اقرار من الوالدة عاتقة توكيل الثعلي في الدعوى 42824717 ضد اسامة زيني ـ 04-03-1445.pdf</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2399,12 +2399,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>مصاريف المزرعة (Excel)</t>
+          <t>مصاريف مزرعة الشيخ أحمد زيني بالوادي (1).xlsx</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>مصاريف المزرعة (Excel)</t>
+          <t>مصاريف مزرعة الشيخ أحمد زيني بالوادي (1).xlsx</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2443,12 +2443,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم إبراء الذمة ـ 22-07-1447</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>حكم نهائي بنقض حكم إبراء الذمة ـ 22-07-1447</t>
+          <t>حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2465,12 +2465,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد (وورد)</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ملخص الشكوى لولي العهد (وورد)</t>
+          <t>ملخص الشكوى لولي العهد.docx</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>طلب إعادة فتح الشكوى المقيدة برقم (199058) وتاريخ 18/06/1445هـ لدى المجلس الأعلى للقضاء ـ 18/06/1445هـ</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>طلب إعادة فتح الشكوى المقيدة برقم (199058) وتاريخ 18/06/1445هـ لدى المجلس الأعلى للقضاء ـ 18/06/1445هـ</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2531,12 +2531,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>تفاصيل إخطار المطالبة المالية بمبلغ 96,779,270</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>تفاصيل إخطار المطالبة المالية بمبلغ 96,779,270</t>
+          <t>تفاصيل إخطار مطالبة مالية من عدنان زيني ضد الشيخ أسامة زيني بمبلغ 96779270 ـ في القضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>التماس في الدعوى ـ نسخة ثانية</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>التماس في الدعوى ـ نسخة ثانية</t>
+          <t>التماس في في دعوى عدنان ضد الشيخ اسامة ـ بطلان حصة شركة احمد زيني التجارية ـ 42824717.docx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2575,12 +2575,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2619,12 +2619,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>مرفق 8 ـ مذكرة أبو راشد ـ 25-04-1443</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>مرفق 8 ـ مذكرة أبو راشد ـ 25-04-1443</t>
+          <t>مرفق رقم 8 ـ مذكرة من المحامي ابو راشد في الدعوى 42824717 ـ 25-04-1443 هـ.pdf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2641,12 +2641,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>صك الحكم رقم (4630548401) وتاريخ 18/06/1446هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، والقاضي بعدم قبول الالتماس المقدم بالطلب رقم (4611037394) وتاريخ 02/06/1446ه</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>صك الحكم رقم (4630548401) وتاريخ 18/06/1446هـ الصادر عن دائرة الاستئناف الثانية بالمحكمة التجارية بجدة، والقاضي بعدم قبول الالتماس المقدم بالطلب رقم (4611037394) وتاريخ 02/06/1446ه</t>
+          <t>صك حكم نهائي الاستئناف الثانية رفض الالتماس ـ 42824717 - 18-06-1446 هـ.pdf</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2685,12 +2685,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>جزء من مصروفات فيلا الوادي</t>
+          <t>جزء من مصروفات فيلا الوادي.pdf</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>جزء من مصروفات فيلا الوادي</t>
+          <t>جزء من مصروفات فيلا الوادي.pdf</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2839,12 +2839,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>طلب النقض من المحكمة العليا ـ 25-02-1445</t>
+          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>طلب النقض من المحكمة العليا ـ 25-02-1445</t>
+          <t>طلب النقض من المحكمة العليا على صك حكم نهائي ضد الشيخ اسامة زيني ـ 42824717 - 25-02-1446هـ تم الرفض.pdf</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3191,12 +3191,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>مذكرة الالتماس ومرفقاتها</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>مذكرة الالتماس ومرفقاتها</t>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3851,12 +3851,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>مصاريف فيلا الوادي (Excel)</t>
+          <t>excelمصاريف فيلا الشيخ أحمد زيني بالوادي.xlsx</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>مصاريف فيلا الوادي (Excel)</t>
+          <t>excelمصاريف فيلا الشيخ أحمد زيني بالوادي.xlsx</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3895,12 +3895,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>مسودة التماس إعادة النظر المقدم على صك الاستئناف الصادر في الدعوى رقم (42824717) وتاريخ 25/12/1442هـ. ـ 25/12/1442هـ</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>مسودة التماس إعادة النظر المقدم على صك الاستئناف الصادر في الدعوى رقم (42824717) وتاريخ 25/12/1442هـ. ـ 25/12/1442هـ</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من الملتمس ضدهم (عدنان وعاتقة)</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>مذكرة جوابية من الملتمس ضدهم (عدنان وعاتقة)</t>
+          <t>مذكرة جوابية من الملتمس ضدهم عدنان احمد زيني وعاتقة الحرازي في الالتماس المقدم برقم 42824717 ـ 15-08-1445.pdf</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4049,12 +4049,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>طلب إعادة فتح الشكوى (صورة)</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>طلب إعادة فتح الشكوى (صورة)</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4071,12 +4071,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4093,12 +4093,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامة</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>مذكرة إلحاقية على التماس الشيخ أسامة</t>
+          <t>مذكرة إلحاقية على التماس الشيخ أسامه زيني ـ القضية 42824717.docx</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4489,12 +4489,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 10-04-1445 ـ مرفق عقود التخارج</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>مذكرة النقض للعليا 10-04-1445 ـ مرفق عقود التخارج</t>
+          <t>مذكرة النقض الى المحكمة العليا بتاريخ 10-04-1445 ـ 42824717 ـ مرفق به عقود التخارج وتقرير احمد زيني رحمه.pdf</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4621,12 +4621,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>مذكرة التماس إلحاقية ـ 08-08-1445</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>مذكرة التماس إلحاقية ـ 08-08-1445</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4779,7 +4779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4843,6 +4843,33 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>4900930</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf | مذكرة التماس من المحامي الشهري بتاريخ 13-07-1445 ـ ومرفقاتها ـ 42824717.pdf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>نفس الحجم - يُحتمل تكرار</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4854,7 +4881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4921,12 +4948,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>تفاصيل دعوى عدنان ضد أسامة ـ موعدها 03-01-1443</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 المجلس الأعلى للقضاء ـ في 13-11-1445 ـ 21-05-2024.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>تفاصيل موعد دعوى عدنان ضد أسامة</t>
+          <t>طلب اعادة فتح شكوى رقم 199058 ـ في 13-11-1445 ـ 21-05-2024.JPG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4948,17 +4975,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447</t>
+          <t>تفاصيل دعوى عدنان ضد أسامة ـ موعدها 03-01-1443</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>مذكرة جوابية على المدعي ـ 02-09-1447 (نسخة)</t>
+          <t>تفاصيل موعد دعوى عدنان ضد أسامة</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5002,17 +5029,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة التماس الحاقية في 8-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>مذكرة جوابية في 16-8-1445 ـ على الحكم النهائي ـ دائرة الاستئناف الثانية ضد الشيخ اسامة زيني ـ 42824717.pdf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5034,7 +5061,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5061,7 +5088,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5088,7 +5115,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5115,7 +5142,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5142,7 +5169,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5169,7 +5196,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5196,7 +5223,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5223,7 +5250,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5245,12 +5272,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 24 يوم 01-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5277,7 +5304,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5304,7 +5331,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5331,7 +5358,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5358,7 +5385,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5385,7 +5412,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5412,7 +5439,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5439,7 +5466,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5461,12 +5488,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 25 يوم 15-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5493,7 +5520,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5520,7 +5547,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5547,7 +5574,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5574,7 +5601,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5601,7 +5628,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5628,7 +5655,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5650,12 +5677,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 26 يوم 29-08-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5682,7 +5709,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5709,7 +5736,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5736,7 +5763,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5763,7 +5790,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5790,7 +5817,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5812,12 +5839,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 27 يوم 20-09-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5844,7 +5871,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5871,7 +5898,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5898,7 +5925,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5925,7 +5952,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5947,12 +5974,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 28 يوم 19-10-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5979,7 +6006,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6006,7 +6033,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6033,7 +6060,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6055,12 +6082,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 29 يوم 03-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6087,7 +6114,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6114,7 +6141,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6136,12 +6163,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 30 يوم 10-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6168,7 +6195,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6190,7 +6217,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
+          <t>ضبط جلسة رقم 31 يوم 17-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6217,17 +6244,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1431 (zip)</t>
+          <t>ضبط جلسة رقم 32 يوم 24-11-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1432 (zip)</t>
+          <t>ضبط جلسة رقم 33 يوم 02-12-1444 هـ للقضية رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6249,7 +6276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1433 (zip)</t>
+          <t>مزرعة الوادي 1432 (zip)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6276,7 +6303,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1434 (zip)</t>
+          <t>مزرعة الوادي 1433 (zip)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6303,7 +6330,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1435 (zip)</t>
+          <t>مزرعة الوادي 1434 (zip)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6330,7 +6357,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1436 (zip)</t>
+          <t>مزرعة الوادي 1435 (zip)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6352,12 +6379,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1432 (zip)</t>
+          <t>مزرعة الوادي 1431 (zip)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1433 (zip)</t>
+          <t>مزرعة الوادي 1436 (zip)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6384,7 +6411,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1434 (zip)</t>
+          <t>مزرعة الوادي 1433 (zip)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6411,7 +6438,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1435 (zip)</t>
+          <t>مزرعة الوادي 1434 (zip)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6438,7 +6465,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1436 (zip)</t>
+          <t>مزرعة الوادي 1435 (zip)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6460,12 +6487,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1433 (zip)</t>
+          <t>مزرعة الوادي 1432 (zip)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1434 (zip)</t>
+          <t>مزرعة الوادي 1436 (zip)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6492,7 +6519,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1435 (zip)</t>
+          <t>مزرعة الوادي 1434 (zip)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6519,7 +6546,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1436 (zip)</t>
+          <t>مزرعة الوادي 1435 (zip)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6541,12 +6568,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1434 (zip)</t>
+          <t>مزرعة الوادي 1433 (zip)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1435 (zip)</t>
+          <t>مزرعة الوادي 1436 (zip)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6573,7 +6600,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1436 (zip)</t>
+          <t>مزرعة الوادي 1435 (zip)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6595,7 +6622,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>مزرعة الوادي 1435 (zip)</t>
+          <t>مزرعة الوادي 1434 (zip)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6622,12 +6649,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>فلة الوادي 1431 (rar)</t>
+          <t>مزرعة الوادي 1435 (zip)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>فلة الوادي 1432 (rar)</t>
+          <t>مزرعة الوادي 1436 (zip)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6654,7 +6681,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>فلة الوادي 1433 (rar)</t>
+          <t>فلة الوادي 1432 (rar)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6681,7 +6708,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>فلة الوادي 2015 (rar)</t>
+          <t>فلة الوادي 1433 (rar)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6703,12 +6730,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>فلة الوادي 1432 (rar)</t>
+          <t>فلة الوادي 1431 (rar)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>فلة الوادي 1433 (rar)</t>
+          <t>فلة الوادي 2015 (rar)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6735,7 +6762,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>فلة الوادي 2015 (rar)</t>
+          <t>فلة الوادي 1433 (rar)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6757,7 +6784,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>فلة الوادي 1433 (rar)</t>
+          <t>فلة الوادي 1432 (rar)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6784,17 +6811,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى</t>
+          <t>فلة الوادي 1433 (rar)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>صورة تقديم الشكوى ـ 243138211</t>
+          <t>فلة الوادي 2015 (rar)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6811,17 +6838,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها</t>
+          <t>صورة تقديم الشكوى</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها ـ 29-10-2024</t>
+          <t>صورة تقديم الشكوى ـ 243138211</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6892,17 +6919,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل (وورد)</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6919,17 +6946,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445</t>
+          <t>صورة تقديم 21-05-2024 (1)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>شكوى لوزير العدل 13-11-1445 ومرفقاتها</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6946,17 +6973,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434</t>
+          <t>صورة تقديم 21-05-2024 (1)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ملحق تنازل عدنان عن حصته ـ 10-02-1434 ـ نسخة</t>
+          <t>صورة تقديم 21-05-2024 (3)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6973,12 +7000,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
+          <t>صورة تقديم 21-05-2024 (2)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>صورة تقديم 21-05-2024 (3)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7000,17 +7027,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (1)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 13-011-1445 ـ 21-05-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (3)</t>
+          <t>شكوى اسامة زيني الى وزير العدل ـ 26-04-1446 ـ 29-10-2024 ـ ومرفقاتها.pdf</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7027,17 +7054,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (2)</t>
+          <t>الشكوى (وورد)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>صورة تقديم 21-05-2024 (3)</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7054,12 +7081,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>الشكوى (وورد)</t>
+          <t>صفحة 1 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>الشكوى الرابعة (وورد)</t>
+          <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -7086,7 +7113,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
+          <t>صفحة 3 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -7108,7 +7135,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>صفحة 1 من تقديم الشكوى</t>
+          <t>صفحة 2 من تقديم الشكوى</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7135,12 +7162,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>صفحة 2 من تقديم الشكوى</t>
+          <t>الشكوى الرابعة (وورد)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>صفحة 3 من تقديم الشكوى</t>
+          <t>الشكوى الرابعة</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7154,33 +7181,6 @@
         </is>
       </c>
       <c r="E85" t="inlineStr">
-        <is>
-          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>الشكوى الرابعة (وورد)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>الشكوى الرابعة</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>[مخرج آلي / Script Output - سماوي]</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
         <is>
           <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>

--- a/zaini_case_audit_output/outputs/excel/02_study_vs_drive_comparison.xlsx
+++ b/zaini_case_audit_output/outputs/excel/02_study_vs_drive_comparison.xlsx
@@ -4737,7 +4737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4765,6 +4765,72 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>وسم مراجعة</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>مستند_جديد_1_14041442.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>موجود في Drive وغير مرتبط برابط في الدراسة (مبدئياً)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>مستند_جديد_3_18121427.pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>موجود في Drive وغير مرتبط برابط في الدراسة (مبدئياً)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>مستند_جديد_2_427036.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>موجود في Drive وغير مرتبط برابط في الدراسة (مبدئياً)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[مخرج آلي / Script Output - سماوي]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>[مخرج آلي يحتاج مراجعة بشرية - وردي]</t>
         </is>
       </c>
     </row>
